--- a/data_output/segur_psd_fit_python/PSD_fit_results.xlsx
+++ b/data_output/segur_psd_fit_python/PSD_fit_results.xlsx
@@ -498,25 +498,25 @@
         <v>165</v>
       </c>
       <c r="C2" t="n">
-        <v>385</v>
+        <v>460</v>
       </c>
       <c r="D2" t="n">
-        <v>-1.919519209984631</v>
+        <v>-2.178262314101336</v>
       </c>
       <c r="E2" t="n">
-        <v>6.646352222023229</v>
+        <v>7.188966785993433</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9880166882373123</v>
+        <v>0.9874272327052629</v>
       </c>
       <c r="G2" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="H2" t="n">
-        <v>-2.919519209984631</v>
+        <v>-3.178262314101336</v>
       </c>
       <c r="I2" t="n">
-        <v>8502461.709674481</v>
+        <v>33657120.98314211</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
@@ -525,7 +525,7 @@
         <v>5000</v>
       </c>
       <c r="L2" t="n">
-        <v>4429474.313386698</v>
+        <v>15451362.52429571</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -543,28 +543,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>95</v>
+        <v>125</v>
       </c>
       <c r="C3" t="n">
-        <v>350</v>
+        <v>330</v>
       </c>
       <c r="D3" t="n">
-        <v>-2.739182076027633</v>
+        <v>-2.796397493529946</v>
       </c>
       <c r="E3" t="n">
-        <v>8.072532486656989</v>
+        <v>8.164359017622759</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9929734699598479</v>
+        <v>0.9908877410115398</v>
       </c>
       <c r="G3" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="H3" t="n">
-        <v>-3.739182076027633</v>
+        <v>-3.796397493529946</v>
       </c>
       <c r="I3" t="n">
-        <v>323707966.6876923</v>
+        <v>408279826.7525871</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
@@ -573,7 +573,7 @@
         <v>5000</v>
       </c>
       <c r="L3" t="n">
-        <v>118176870.9341352</v>
+        <v>146002071.4790114</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -591,28 +591,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="C4" t="n">
         <v>480</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.67106150944134</v>
+        <v>-1.735140565387896</v>
       </c>
       <c r="E4" t="n">
-        <v>5.896144627132704</v>
+        <v>5.961682977544652</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9696822374227052</v>
+        <v>0.9608973398845442</v>
       </c>
       <c r="G4" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.671061509441341</v>
+        <v>-2.735140565387896</v>
       </c>
       <c r="I4" t="n">
-        <v>1315639.981915651</v>
+        <v>1588611.275448175</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -621,7 +621,7 @@
         <v>5000</v>
       </c>
       <c r="L4" t="n">
-        <v>787307.4136762404</v>
+        <v>915551.5701158018</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -645,22 +645,22 @@
         <v>560</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.98298364129834</v>
+        <v>-1.969281003697001</v>
       </c>
       <c r="E5" t="n">
-        <v>6.848251205382933</v>
+        <v>6.794419287454688</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9962128598531879</v>
+        <v>0.9944016755275872</v>
       </c>
       <c r="G5" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.98298364129834</v>
+        <v>-2.969281003697001</v>
       </c>
       <c r="I5" t="n">
-        <v>13982033.45297438</v>
+        <v>12266678.39068415</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
@@ -669,7 +669,7 @@
         <v>5000</v>
       </c>
       <c r="L5" t="n">
-        <v>7051007.640846008</v>
+        <v>6229013.396386933</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -693,22 +693,22 @@
         <v>410</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.576619420139119</v>
+        <v>-2.537141017015231</v>
       </c>
       <c r="E6" t="n">
-        <v>7.932215013029039</v>
+        <v>7.810628033600369</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9917455917646081</v>
+        <v>0.9923810700594311</v>
       </c>
       <c r="G6" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H6" t="n">
-        <v>-3.576619420139119</v>
+        <v>-3.537141017015231</v>
       </c>
       <c r="I6" t="n">
-        <v>220427253.1853068</v>
+        <v>164048642.1557541</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -717,7 +717,7 @@
         <v>5000</v>
       </c>
       <c r="L6" t="n">
-        <v>85549014.8826395</v>
+        <v>64658858.52931897</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -741,22 +741,22 @@
         <v>585</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.470704947074662</v>
+        <v>-1.468227363734859</v>
       </c>
       <c r="E7" t="n">
-        <v>5.363330702665392</v>
+        <v>5.347549482326052</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9865468308222398</v>
+        <v>0.9876996299709244</v>
       </c>
       <c r="G7" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.470704947074662</v>
+        <v>-2.468227363734859</v>
       </c>
       <c r="I7" t="n">
-        <v>339512.8810262204</v>
+        <v>326845.7153969181</v>
       </c>
       <c r="J7" t="n">
         <v>1</v>
@@ -765,7 +765,7 @@
         <v>5000</v>
       </c>
       <c r="L7" t="n">
-        <v>230849.5998943134</v>
+        <v>222611.641573885</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -789,22 +789,22 @@
         <v>245</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.765263164794791</v>
+        <v>-1.707671168080249</v>
       </c>
       <c r="E8" t="n">
-        <v>5.343845860830124</v>
+        <v>5.211815504510901</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9939172884363451</v>
+        <v>0.9927208015648868</v>
       </c>
       <c r="G8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.765263164794791</v>
+        <v>-2.70767116808025</v>
       </c>
       <c r="I8" t="n">
-        <v>389632.6298958096</v>
+        <v>278112.0142317772</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
@@ -813,7 +813,7 @@
         <v>5000</v>
       </c>
       <c r="L8" t="n">
-        <v>220722.0558307586</v>
+        <v>162860.3242115948</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -837,22 +837,22 @@
         <v>220</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.15057100900288</v>
+        <v>-2.074025886910791</v>
       </c>
       <c r="E9" t="n">
-        <v>6.080429843520262</v>
+        <v>5.906229229854062</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9946449592773108</v>
+        <v>0.9930485588491925</v>
       </c>
       <c r="G9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.15057100900288</v>
+        <v>-3.074025886910791</v>
       </c>
       <c r="I9" t="n">
-        <v>2588115.361490024</v>
+        <v>1671257.628327265</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
@@ -861,7 +861,7 @@
         <v>5000</v>
       </c>
       <c r="L9" t="n">
-        <v>1203454.953099421</v>
+        <v>805803.6320993932</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>

--- a/data_output/segur_psd_fit_python/PSD_fit_results.xlsx
+++ b/data_output/segur_psd_fit_python/PSD_fit_results.xlsx
@@ -495,28 +495,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>165</v>
+        <v>115</v>
       </c>
       <c r="C2" t="n">
-        <v>460</v>
+        <v>480</v>
       </c>
       <c r="D2" t="n">
-        <v>-2.178262314101336</v>
+        <v>-1.731465148871292</v>
       </c>
       <c r="E2" t="n">
-        <v>7.188966785993433</v>
+        <v>7.126805998778096</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9874272327052629</v>
+        <v>0.9960409411613318</v>
       </c>
       <c r="G2" t="n">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="H2" t="n">
-        <v>-3.178262314101336</v>
+        <v>-2.731465148871292</v>
       </c>
       <c r="I2" t="n">
-        <v>33657120.98314211</v>
+        <v>23185675.49525659</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
@@ -525,7 +525,7 @@
         <v>5000</v>
       </c>
       <c r="L2" t="n">
-        <v>15451362.52429571</v>
+        <v>13390778.54268692</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -543,28 +543,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="C3" t="n">
-        <v>330</v>
+        <v>485</v>
       </c>
       <c r="D3" t="n">
-        <v>-2.796397493529946</v>
+        <v>-2.842457722625832</v>
       </c>
       <c r="E3" t="n">
-        <v>8.164359017622759</v>
+        <v>9.355819158274613</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9908877410115398</v>
+        <v>0.9920040065582078</v>
       </c>
       <c r="G3" t="n">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="H3" t="n">
-        <v>-3.796397493529946</v>
+        <v>-3.842457722625832</v>
       </c>
       <c r="I3" t="n">
-        <v>408279826.7525871</v>
+        <v>6449308803.840319</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
@@ -573,7 +573,7 @@
         <v>5000</v>
       </c>
       <c r="L3" t="n">
-        <v>146002071.4790114</v>
+        <v>2268919868.994609</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -591,28 +591,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="C4" t="n">
-        <v>480</v>
+        <v>645</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.735140565387896</v>
+        <v>-1.481507510024812</v>
       </c>
       <c r="E4" t="n">
-        <v>5.961682977544652</v>
+        <v>6.343866283055963</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9608973398845442</v>
+        <v>0.9922404849184541</v>
       </c>
       <c r="G4" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.735140565387896</v>
+        <v>-2.481507510024812</v>
       </c>
       <c r="I4" t="n">
-        <v>1588611.275448175</v>
+        <v>3270168.571735642</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -621,7 +621,7 @@
         <v>5000</v>
       </c>
       <c r="L4" t="n">
-        <v>915551.5701158018</v>
+        <v>2207317.69657213</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -639,28 +639,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>135</v>
+        <v>240</v>
       </c>
       <c r="C5" t="n">
-        <v>560</v>
+        <v>1090</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.969281003697001</v>
+        <v>-1.822126548009346</v>
       </c>
       <c r="E5" t="n">
-        <v>6.794419287454688</v>
+        <v>7.77333918700424</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9944016755275872</v>
+        <v>0.9964361603112224</v>
       </c>
       <c r="G5" t="n">
-        <v>63</v>
+        <v>163</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.969281003697001</v>
+        <v>-2.822126548009346</v>
       </c>
       <c r="I5" t="n">
-        <v>12266678.39068415</v>
+        <v>108122909.2655227</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
@@ -669,7 +669,7 @@
         <v>5000</v>
       </c>
       <c r="L5" t="n">
-        <v>6229013.396386933</v>
+        <v>59338847.62730841</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -687,28 +687,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>115</v>
+        <v>165</v>
       </c>
       <c r="C6" t="n">
-        <v>410</v>
+        <v>650</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.537141017015231</v>
+        <v>-2.78302020206548</v>
       </c>
       <c r="E6" t="n">
-        <v>7.810628033600369</v>
+        <v>9.610784685509248</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9923810700594311</v>
+        <v>0.9926052628322157</v>
       </c>
       <c r="G6" t="n">
-        <v>42</v>
+        <v>89</v>
       </c>
       <c r="H6" t="n">
-        <v>-3.537141017015231</v>
+        <v>-3.78302020206548</v>
       </c>
       <c r="I6" t="n">
-        <v>164048642.1557541</v>
+        <v>11357978556.5852</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -717,7 +717,7 @@
         <v>5000</v>
       </c>
       <c r="L6" t="n">
-        <v>64658858.52931897</v>
+        <v>4081169999.261545</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -735,28 +735,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>200</v>
+        <v>270</v>
       </c>
       <c r="C7" t="n">
-        <v>585</v>
+        <v>1580</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.468227363734859</v>
+        <v>-1.7005080254938</v>
       </c>
       <c r="E7" t="n">
-        <v>5.347549482326052</v>
+        <v>7.359041380922454</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9876996299709244</v>
+        <v>0.9896219000377395</v>
       </c>
       <c r="G7" t="n">
-        <v>43</v>
+        <v>208</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.468227363734859</v>
+        <v>-2.7005080254938</v>
       </c>
       <c r="I7" t="n">
-        <v>326845.7153969181</v>
+        <v>38870494.60658217</v>
       </c>
       <c r="J7" t="n">
         <v>1</v>
@@ -765,7 +765,7 @@
         <v>5000</v>
       </c>
       <c r="L7" t="n">
-        <v>222611.641573885</v>
+        <v>22858154.20718287</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -783,28 +783,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>95</v>
+        <v>250</v>
       </c>
       <c r="C8" t="n">
-        <v>245</v>
+        <v>985</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.707671168080249</v>
+        <v>-1.653087868011876</v>
       </c>
       <c r="E8" t="n">
-        <v>5.211815504510901</v>
+        <v>6.688512081847955</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9927208015648868</v>
+        <v>0.9972704914021669</v>
       </c>
       <c r="G8" t="n">
-        <v>17</v>
+        <v>112</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.70767116808025</v>
+        <v>-2.653087868011876</v>
       </c>
       <c r="I8" t="n">
-        <v>278112.0142317772</v>
+        <v>8068782.71493183</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
@@ -813,7 +813,7 @@
         <v>5000</v>
       </c>
       <c r="L8" t="n">
-        <v>162860.3242115948</v>
+        <v>4881033.050593001</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -831,28 +831,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>95</v>
+        <v>125</v>
       </c>
       <c r="C9" t="n">
-        <v>220</v>
+        <v>430</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.074025886910791</v>
+        <v>-2.585063960078156</v>
       </c>
       <c r="E9" t="n">
-        <v>5.906229229854062</v>
+        <v>8.329063521893604</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9930485588491925</v>
+        <v>0.9928380729994105</v>
       </c>
       <c r="G9" t="n">
-        <v>15</v>
+        <v>53</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.074025886910791</v>
+        <v>-3.585063960078156</v>
       </c>
       <c r="I9" t="n">
-        <v>1671257.628327265</v>
+        <v>551486410.0415778</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
@@ -861,7 +861,7 @@
         <v>5000</v>
       </c>
       <c r="L9" t="n">
-        <v>805803.6320993932</v>
+        <v>213335692.4266339</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -879,28 +879,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>260</v>
+        <v>245</v>
       </c>
       <c r="C10" t="n">
-        <v>770</v>
+        <v>1420</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.9805502335947731</v>
+        <v>-1.490056869613978</v>
       </c>
       <c r="E10" t="n">
-        <v>3.12020778704925</v>
+        <v>6.186884541687744</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9700440889465617</v>
+        <v>0.9899488406895184</v>
       </c>
       <c r="G10" t="n">
-        <v>5</v>
+        <v>123</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.980550233594773</v>
+        <v>-2.490056869613977</v>
       </c>
       <c r="I10" t="n">
-        <v>1293.235550072013</v>
+        <v>2291328.65167865</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -909,7 +909,7 @@
         <v>5000</v>
       </c>
       <c r="L10" t="n">
-        <v>1318.576303940319</v>
+        <v>1537741.038473087</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
